--- a/02_Output/Descriptives/Table_exposure_commune_PM25_O3_summary.xlsx
+++ b/02_Output/Descriptives/Table_exposure_commune_PM25_O3_summary.xlsx
@@ -1,23 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10802"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jd/Library/CloudStorage/OneDrive-UniversidadCatólicadeChile(2)/ANID Iniciación_2024_2027/Contamination_PTB_G-Formula/02_Output/Descriptives/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C634D69-AB5A-F245-9A06-240535945D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="660" windowWidth="25400" windowHeight="19600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Kriging_OK" sheetId="1" r:id="rId1"/>
     <sheet name="IDW" sheetId="2" r:id="rId2"/>
     <sheet name="Kriging_IDW_label" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1902,8 +1896,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1951,21 +1945,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2003,7 +1989,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2037,7 +2023,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2072,10 +2057,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2248,11 +2232,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2302,7 +2286,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>13101</v>
       </c>
@@ -2352,7 +2336,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>13102</v>
       </c>
@@ -2402,7 +2386,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>13103</v>
       </c>
@@ -2452,7 +2436,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>13104</v>
       </c>
@@ -2502,7 +2486,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>13105</v>
       </c>
@@ -2552,7 +2536,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>13106</v>
       </c>
@@ -2602,7 +2586,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>13107</v>
       </c>
@@ -2652,7 +2636,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>13108</v>
       </c>
@@ -2702,7 +2686,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>13109</v>
       </c>
@@ -2752,7 +2736,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>13110</v>
       </c>
@@ -2802,7 +2786,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16">
       <c r="A12">
         <v>13111</v>
       </c>
@@ -2852,7 +2836,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16">
       <c r="A13">
         <v>13112</v>
       </c>
@@ -2902,7 +2886,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16">
       <c r="A14">
         <v>13113</v>
       </c>
@@ -2952,7 +2936,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16">
       <c r="A15">
         <v>13114</v>
       </c>
@@ -3002,7 +2986,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16">
       <c r="A16">
         <v>13115</v>
       </c>
@@ -3052,7 +3036,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16">
       <c r="A17">
         <v>13116</v>
       </c>
@@ -3102,7 +3086,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16">
       <c r="A18">
         <v>13117</v>
       </c>
@@ -3152,7 +3136,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16">
       <c r="A19">
         <v>13118</v>
       </c>
@@ -3202,7 +3186,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16">
       <c r="A20">
         <v>13119</v>
       </c>
@@ -3252,7 +3236,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16">
       <c r="A21">
         <v>13120</v>
       </c>
@@ -3302,7 +3286,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16">
       <c r="A22">
         <v>13121</v>
       </c>
@@ -3352,7 +3336,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16">
       <c r="A23">
         <v>13122</v>
       </c>
@@ -3402,7 +3386,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16">
       <c r="A24">
         <v>13123</v>
       </c>
@@ -3452,7 +3436,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16">
       <c r="A25">
         <v>13124</v>
       </c>
@@ -3502,7 +3486,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16">
       <c r="A26">
         <v>13125</v>
       </c>
@@ -3552,7 +3536,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16">
       <c r="A27">
         <v>13126</v>
       </c>
@@ -3602,7 +3586,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16">
       <c r="A28">
         <v>13127</v>
       </c>
@@ -3652,7 +3636,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16">
       <c r="A29">
         <v>13128</v>
       </c>
@@ -3702,7 +3686,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16">
       <c r="A30">
         <v>13129</v>
       </c>
@@ -3752,7 +3736,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16">
       <c r="A31">
         <v>13130</v>
       </c>
@@ -3802,7 +3786,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16">
       <c r="A32">
         <v>13131</v>
       </c>
@@ -3852,7 +3836,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16">
       <c r="A33">
         <v>13132</v>
       </c>
@@ -3902,7 +3886,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16">
       <c r="A34">
         <v>13201</v>
       </c>
@@ -3958,11 +3942,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4012,7 +3996,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>13101</v>
       </c>
@@ -4062,7 +4046,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>13102</v>
       </c>
@@ -4112,7 +4096,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>13103</v>
       </c>
@@ -4162,7 +4146,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>13104</v>
       </c>
@@ -4212,7 +4196,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>13105</v>
       </c>
@@ -4262,7 +4246,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>13106</v>
       </c>
@@ -4312,7 +4296,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>13107</v>
       </c>
@@ -4362,7 +4346,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>13108</v>
       </c>
@@ -4412,7 +4396,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>13109</v>
       </c>
@@ -4462,7 +4446,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>13110</v>
       </c>
@@ -4512,7 +4496,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16">
       <c r="A12">
         <v>13111</v>
       </c>
@@ -4562,7 +4546,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16">
       <c r="A13">
         <v>13112</v>
       </c>
@@ -4612,7 +4596,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16">
       <c r="A14">
         <v>13113</v>
       </c>
@@ -4662,7 +4646,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16">
       <c r="A15">
         <v>13114</v>
       </c>
@@ -4712,7 +4696,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16">
       <c r="A16">
         <v>13115</v>
       </c>
@@ -4762,7 +4746,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16">
       <c r="A17">
         <v>13116</v>
       </c>
@@ -4812,7 +4796,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16">
       <c r="A18">
         <v>13117</v>
       </c>
@@ -4862,7 +4846,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16">
       <c r="A19">
         <v>13118</v>
       </c>
@@ -4912,7 +4896,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16">
       <c r="A20">
         <v>13119</v>
       </c>
@@ -4962,7 +4946,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16">
       <c r="A21">
         <v>13120</v>
       </c>
@@ -5012,7 +4996,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16">
       <c r="A22">
         <v>13121</v>
       </c>
@@ -5062,7 +5046,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16">
       <c r="A23">
         <v>13122</v>
       </c>
@@ -5112,7 +5096,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16">
       <c r="A24">
         <v>13123</v>
       </c>
@@ -5162,7 +5146,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16">
       <c r="A25">
         <v>13124</v>
       </c>
@@ -5212,7 +5196,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16">
       <c r="A26">
         <v>13125</v>
       </c>
@@ -5262,7 +5246,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16">
       <c r="A27">
         <v>13126</v>
       </c>
@@ -5312,7 +5296,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16">
       <c r="A28">
         <v>13127</v>
       </c>
@@ -5362,7 +5346,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16">
       <c r="A29">
         <v>13128</v>
       </c>
@@ -5412,7 +5396,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16">
       <c r="A30">
         <v>13129</v>
       </c>
@@ -5462,7 +5446,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16">
       <c r="A31">
         <v>13130</v>
       </c>
@@ -5512,7 +5496,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16">
       <c r="A32">
         <v>13131</v>
       </c>
@@ -5562,7 +5546,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16">
       <c r="A33">
         <v>13132</v>
       </c>
@@ -5612,7 +5596,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16">
       <c r="A34">
         <v>13201</v>
       </c>
@@ -5668,11 +5652,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5722,7 +5706,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>13101</v>
       </c>
@@ -5772,7 +5756,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>13101</v>
       </c>
@@ -5822,7 +5806,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>13102</v>
       </c>
@@ -5872,7 +5856,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>13102</v>
       </c>
@@ -5922,7 +5906,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>13103</v>
       </c>
@@ -5972,7 +5956,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>13103</v>
       </c>
@@ -6022,7 +6006,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>13104</v>
       </c>
@@ -6072,7 +6056,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>13104</v>
       </c>
@@ -6122,7 +6106,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>13105</v>
       </c>
@@ -6172,7 +6156,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>13105</v>
       </c>
@@ -6222,7 +6206,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16">
       <c r="A12">
         <v>13106</v>
       </c>
@@ -6272,7 +6256,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16">
       <c r="A13">
         <v>13106</v>
       </c>
@@ -6322,7 +6306,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16">
       <c r="A14">
         <v>13107</v>
       </c>
@@ -6372,7 +6356,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16">
       <c r="A15">
         <v>13107</v>
       </c>
@@ -6422,7 +6406,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16">
       <c r="A16">
         <v>13108</v>
       </c>
@@ -6472,7 +6456,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16">
       <c r="A17">
         <v>13108</v>
       </c>
@@ -6522,7 +6506,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16">
       <c r="A18">
         <v>13109</v>
       </c>
@@ -6572,7 +6556,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16">
       <c r="A19">
         <v>13109</v>
       </c>
@@ -6622,7 +6606,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16">
       <c r="A20">
         <v>13110</v>
       </c>
@@ -6672,7 +6656,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16">
       <c r="A21">
         <v>13110</v>
       </c>
@@ -6722,7 +6706,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16">
       <c r="A22">
         <v>13111</v>
       </c>
@@ -6772,7 +6756,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16">
       <c r="A23">
         <v>13111</v>
       </c>
@@ -6822,7 +6806,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16">
       <c r="A24">
         <v>13112</v>
       </c>
@@ -6872,7 +6856,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16">
       <c r="A25">
         <v>13112</v>
       </c>
@@ -6922,7 +6906,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16">
       <c r="A26">
         <v>13113</v>
       </c>
@@ -6972,7 +6956,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16">
       <c r="A27">
         <v>13113</v>
       </c>
@@ -7022,7 +7006,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16">
       <c r="A28">
         <v>13114</v>
       </c>
@@ -7072,7 +7056,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16">
       <c r="A29">
         <v>13114</v>
       </c>
@@ -7122,7 +7106,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16">
       <c r="A30">
         <v>13115</v>
       </c>
@@ -7172,7 +7156,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16">
       <c r="A31">
         <v>13115</v>
       </c>
@@ -7222,7 +7206,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16">
       <c r="A32">
         <v>13116</v>
       </c>
@@ -7272,7 +7256,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16">
       <c r="A33">
         <v>13116</v>
       </c>
@@ -7322,7 +7306,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16">
       <c r="A34">
         <v>13117</v>
       </c>
@@ -7372,7 +7356,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16">
       <c r="A35">
         <v>13117</v>
       </c>
@@ -7422,7 +7406,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16">
       <c r="A36">
         <v>13118</v>
       </c>
@@ -7472,7 +7456,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16">
       <c r="A37">
         <v>13118</v>
       </c>
@@ -7522,7 +7506,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16">
       <c r="A38">
         <v>13119</v>
       </c>
@@ -7572,7 +7556,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16">
       <c r="A39">
         <v>13119</v>
       </c>
@@ -7622,7 +7606,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16">
       <c r="A40">
         <v>13120</v>
       </c>
@@ -7672,7 +7656,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16">
       <c r="A41">
         <v>13120</v>
       </c>
@@ -7722,7 +7706,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16">
       <c r="A42">
         <v>13121</v>
       </c>
@@ -7772,7 +7756,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16">
       <c r="A43">
         <v>13121</v>
       </c>
@@ -7822,7 +7806,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16">
       <c r="A44">
         <v>13122</v>
       </c>
@@ -7872,7 +7856,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16">
       <c r="A45">
         <v>13122</v>
       </c>
@@ -7922,7 +7906,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16">
       <c r="A46">
         <v>13123</v>
       </c>
@@ -7972,7 +7956,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16">
       <c r="A47">
         <v>13123</v>
       </c>
@@ -8022,7 +8006,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16">
       <c r="A48">
         <v>13124</v>
       </c>
@@ -8072,7 +8056,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:16">
       <c r="A49">
         <v>13124</v>
       </c>
@@ -8122,7 +8106,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:16">
       <c r="A50">
         <v>13125</v>
       </c>
@@ -8172,7 +8156,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:16">
       <c r="A51">
         <v>13125</v>
       </c>
@@ -8222,7 +8206,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:16">
       <c r="A52">
         <v>13126</v>
       </c>
@@ -8272,7 +8256,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:16">
       <c r="A53">
         <v>13126</v>
       </c>
@@ -8322,7 +8306,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:16">
       <c r="A54">
         <v>13127</v>
       </c>
@@ -8372,7 +8356,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:16">
       <c r="A55">
         <v>13127</v>
       </c>
@@ -8422,7 +8406,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:16">
       <c r="A56">
         <v>13128</v>
       </c>
@@ -8472,7 +8456,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:16">
       <c r="A57">
         <v>13128</v>
       </c>
@@ -8522,7 +8506,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:16">
       <c r="A58">
         <v>13129</v>
       </c>
@@ -8572,7 +8556,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:16">
       <c r="A59">
         <v>13129</v>
       </c>
@@ -8622,7 +8606,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:16">
       <c r="A60">
         <v>13130</v>
       </c>
@@ -8672,7 +8656,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:16">
       <c r="A61">
         <v>13130</v>
       </c>
@@ -8722,7 +8706,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:16">
       <c r="A62">
         <v>13131</v>
       </c>
@@ -8772,7 +8756,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:16">
       <c r="A63">
         <v>13131</v>
       </c>
@@ -8822,7 +8806,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:16">
       <c r="A64">
         <v>13132</v>
       </c>
@@ -8872,7 +8856,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:16">
       <c r="A65">
         <v>13132</v>
       </c>
@@ -8922,7 +8906,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:16">
       <c r="A66">
         <v>13201</v>
       </c>
@@ -8972,7 +8956,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:16">
       <c r="A67">
         <v>13201</v>
       </c>
